--- a/content.xlsx
+++ b/content.xlsx
@@ -413,7 +413,7 @@
         <v>reference-id</v>
       </c>
       <c r="E1" t="str">
-        <v>type</v>
+        <v>section</v>
       </c>
       <c r="F1" t="str">
         <v>meta-keys</v>
